--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_1405.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_1405.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1690,6 +1690,9 @@
           <t>1405-20-24</t>
         </is>
       </c>
+      <c r="G22" t="n">
+        <v>1.48</v>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>1405-20-24</t>
@@ -1702,12 +1705,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | TAPDRILL@BORE = Air-Way per-size tap drill -20 1.48 (A1)</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
